--- a/braph2individualconnectome/pipelines/neuroimaging conversion PDFs/Example data NIfTI PDF shape covariation/reference_data/pdf_gmprob/sub-0004_ses-01_GMprob_pdf.xlsx
+++ b/braph2individualconnectome/pipelines/neuroimaging conversion PDFs/Example data NIfTI PDF shape covariation/reference_data/pdf_gmprob/sub-0004_ses-01_GMprob_pdf.xlsx
@@ -1,7 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fileVersion appName="libxl" rupBuild="4.6.0"/>
   <workbookPr/>
   <bookViews>
     <workbookView activeTab="0"/>
@@ -12328,7 +12327,7 @@
         <v>0</v>
       </c>
       <c r="BP34" s="0">
-        <v>0.022045855379188691</v>
+        <v>0.02204585537918869</v>
       </c>
       <c r="BQ34" s="0">
         <v>0</v>
@@ -12645,7 +12644,7 @@
         <v>0</v>
       </c>
       <c r="BA35" s="0">
-        <v>0.062912865681032063</v>
+        <v>0.062912865681032062</v>
       </c>
       <c r="BB35" s="0">
         <v>0</v>
@@ -13489,7 +13488,7 @@
         <v>0</v>
       </c>
       <c r="CO37" s="0">
-        <v>0.066120074054482878</v>
+        <v>0.066120074054482877</v>
       </c>
       <c r="CP37" s="0">
         <v>0</v>
@@ -14201,7 +14200,7 @@
         <v>0</v>
       </c>
       <c r="CK39" s="0">
-        <v>0.017028522775649199</v>
+        <v>0.017028522775649198</v>
       </c>
       <c r="CL39" s="0">
         <v>0</v>
@@ -14563,7 +14562,7 @@
         <v>0</v>
       </c>
       <c r="CK40" s="0">
-        <v>0.017028522775649199</v>
+        <v>0.017028522775649198</v>
       </c>
       <c r="CL40" s="0">
         <v>0.018946570670708585</v>
@@ -14913,7 +14912,7 @@
         <v>0</v>
       </c>
       <c r="CG41" s="0">
-        <v>0.709094132246059</v>
+        <v>0.70909413224605899</v>
       </c>
       <c r="CH41" s="0">
         <v>0.95402146548297784</v>
@@ -15227,7 +15226,7 @@
         <v>6.6798941798941742</v>
       </c>
       <c r="BQ42" s="0">
-        <v>1.7587939698492448</v>
+        <v>1.7587939698492447</v>
       </c>
       <c r="BR42" s="0">
         <v>0.41172196657786353</v>
@@ -15903,7 +15902,7 @@
         <v>7.9659133012226686</v>
       </c>
       <c r="BA44" s="0">
-        <v>1.0066058508965075</v>
+        <v>1.0066058508965074</v>
       </c>
       <c r="BB44" s="0">
         <v>2.4837374334713163</v>
@@ -16145,7 +16144,7 @@
         <v>0.53276505061267931</v>
       </c>
       <c r="M45" s="0">
-        <v>0.91476091476091404</v>
+        <v>0.91476091476091403</v>
       </c>
       <c r="N45" s="0">
         <v>0.12461059190031142</v>
@@ -16271,7 +16270,7 @@
         <v>6.6232998225901785</v>
       </c>
       <c r="BC45" s="0">
-        <v>0.050787201625190404</v>
+        <v>0.050787201625190403</v>
       </c>
       <c r="BD45" s="0">
         <v>13.278520041109958</v>
@@ -16672,7 +16671,7 @@
         <v>7.8689631881121169</v>
       </c>
       <c r="BP46" s="0">
-        <v>0.022045855379188691</v>
+        <v>0.02204585537918869</v>
       </c>
       <c r="BQ46" s="0">
         <v>11.593682699210328</v>
@@ -16693,7 +16692,7 @@
         <v>2.4570024570024547</v>
       </c>
       <c r="BW46" s="0">
-        <v>4.7807017543859614</v>
+        <v>4.7807017543859613</v>
       </c>
       <c r="BX46" s="0">
         <v>4.7538914598233024</v>
@@ -16723,7 +16722,7 @@
         <v>0.86355785837651045</v>
       </c>
       <c r="CG46" s="0">
-        <v>9.4664066654848345</v>
+        <v>9.4664066654848344</v>
       </c>
       <c r="CH46" s="0">
         <v>10.401484033390743</v>
@@ -17261,7 +17260,7 @@
         <v>12.178308823529401</v>
       </c>
       <c r="W48" s="0">
-        <v>6.769230769230763</v>
+        <v>6.7692307692307629</v>
       </c>
       <c r="X48" s="0">
         <v>9.2097782831153978</v>
@@ -17435,7 +17434,7 @@
         <v>6.4566929133858206</v>
       </c>
       <c r="CC48" s="0">
-        <v>1.8372703412073475</v>
+        <v>1.8372703412073474</v>
       </c>
       <c r="CD48" s="0">
         <v>8.6923076923076845</v>
@@ -17537,7 +17536,7 @@
         <v>5.6910569105691007</v>
       </c>
       <c r="DK48" s="0">
-        <v>0.62413314840499246</v>
+        <v>0.62413314840499245</v>
       </c>
       <c r="DL48" s="0">
         <v>0.91383812010443788</v>
@@ -17617,7 +17616,7 @@
         <v>14.320835894283947</v>
       </c>
       <c r="U49" s="0">
-        <v>5.8561070831009428</v>
+        <v>5.8561070831009427</v>
       </c>
       <c r="V49" s="0">
         <v>14.430147058823515</v>
@@ -17728,7 +17727,7 @@
         <v>10.876699484294411</v>
       </c>
       <c r="BF49" s="0">
-        <v>6.4139941690962044</v>
+        <v>6.4139941690962043</v>
       </c>
       <c r="BG49" s="0">
         <v>0.90573012939001774</v>
@@ -17809,7 +17808,7 @@
         <v>17.271157167530209</v>
       </c>
       <c r="CG49" s="0">
-        <v>0.24818294628611926</v>
+        <v>0.24818294628611925</v>
       </c>
       <c r="CH49" s="0">
         <v>0.17225387571220338</v>
@@ -17824,7 +17823,7 @@
         <v>0.9621115368241796</v>
       </c>
       <c r="CL49" s="0">
-        <v>0.96627510420613783</v>
+        <v>0.96627510420613782</v>
       </c>
       <c r="CM49" s="0">
         <v>0.55897149245388433</v>
@@ -17869,19 +17868,19 @@
         <v>0.51270100209741276</v>
       </c>
       <c r="DA49" s="0">
-        <v>0.36023054755043194</v>
+        <v>0.36023054755043193</v>
       </c>
       <c r="DB49" s="0">
         <v>0</v>
       </c>
       <c r="DC49" s="0">
-        <v>16.255051638976188</v>
+        <v>16.255051638976187</v>
       </c>
       <c r="DD49" s="0">
         <v>2.7140255009107443</v>
       </c>
       <c r="DE49" s="0">
-        <v>6.3798936684388528</v>
+        <v>6.3798936684388527</v>
       </c>
       <c r="DF49" s="0">
         <v>1.3803680981595079</v>
@@ -17976,7 +17975,7 @@
         <v>12.607968793535793</v>
       </c>
       <c r="T50" s="0">
-        <v>8.3384552345830692</v>
+        <v>8.3384552345830691</v>
       </c>
       <c r="U50" s="0">
         <v>1.9520356943669808</v>
@@ -18084,7 +18083,7 @@
         <v>13.268156424580996</v>
       </c>
       <c r="BD50" s="0">
-        <v>0.020554984583761545</v>
+        <v>0.020554984583761544</v>
       </c>
       <c r="BE50" s="0">
         <v>7.3136427566807249</v>
@@ -18168,7 +18167,7 @@
         <v>9.7142857142857064</v>
       </c>
       <c r="CF50" s="0">
-        <v>17.789291882556118</v>
+        <v>17.789291882556117</v>
       </c>
       <c r="CG50" s="0">
         <v>0.017727353306151376</v>
@@ -18545,7 +18544,7 @@
         <v>0.18975332068311179</v>
       </c>
       <c r="CK51" s="0">
-        <v>0.017028522775649199</v>
+        <v>0.017028522775649198</v>
       </c>
       <c r="CL51" s="0">
         <v>0.037893141341417171</v>
@@ -18602,7 +18601,7 @@
         <v>6.9375841939829295</v>
       </c>
       <c r="DD51" s="0">
-        <v>0.12750455373406181</v>
+        <v>0.1275045537340618</v>
       </c>
       <c r="DE51" s="0">
         <v>0.91831802803286522</v>
@@ -18655,7 +18654,7 @@
         <v>0.49995901975247892</v>
       </c>
       <c r="E52" s="0">
-        <v>0.065414447247920699</v>
+        <v>0.065414447247920698</v>
       </c>
       <c r="F52" s="0">
         <v>0.12051304123267616</v>
@@ -18667,7 +18666,7 @@
         <v>7.568876778686036</v>
       </c>
       <c r="I52" s="0">
-        <v>2.2591362126245827</v>
+        <v>2.2591362126245826</v>
       </c>
       <c r="J52" s="0">
         <v>15.327066948014565</v>
@@ -18967,7 +18966,7 @@
         <v>0.018214936247723117</v>
       </c>
       <c r="DE52" s="0">
-        <v>0.19333011116481375</v>
+        <v>0.19333011116481374</v>
       </c>
       <c r="DF52" s="0">
         <v>0</v>
@@ -18991,7 +18990,7 @@
         <v>15.013054830287192</v>
       </c>
       <c r="DM52" s="0">
-        <v>3.8461538461538432</v>
+        <v>3.8461538461538431</v>
       </c>
       <c r="DN52" s="0">
         <v>0.19531249999999983</v>
@@ -19230,7 +19229,7 @@
         <v>0.087719298245613961</v>
       </c>
       <c r="BX53" s="0">
-        <v>0.33655868742111878</v>
+        <v>0.33655868742111877</v>
       </c>
       <c r="BY53" s="0">
         <v>0</v>
@@ -19299,7 +19298,7 @@
         <v>0.020024028834601505</v>
       </c>
       <c r="CU53" s="0">
-        <v>13.473053892215559</v>
+        <v>13.473053892215558</v>
       </c>
       <c r="CV53" s="0">
         <v>18.283582089552223</v>
@@ -19409,7 +19408,7 @@
         <v>0.37383177570093429</v>
       </c>
       <c r="O54" s="0">
-        <v>3.084832904884316</v>
+        <v>3.0848329048843159</v>
       </c>
       <c r="P54" s="0">
         <v>1.2625831769322631</v>
@@ -19589,7 +19588,7 @@
         <v>0</v>
       </c>
       <c r="BW54" s="0">
-        <v>0.043859649122806981</v>
+        <v>0.04385964912280698</v>
       </c>
       <c r="BX54" s="0">
         <v>0</v>
@@ -19756,7 +19755,7 @@
         <v>0.01661129568106311</v>
       </c>
       <c r="J55" s="0">
-        <v>0.97832342221369562</v>
+        <v>0.97832342221369561</v>
       </c>
       <c r="K55" s="0">
         <v>0</v>
@@ -20142,7 +20141,7 @@
         <v>8.4876543209876463</v>
       </c>
       <c r="R56" s="0">
-        <v>6.3360881542699668</v>
+        <v>6.3360881542699667</v>
       </c>
       <c r="S56" s="0">
         <v>0.18110894399554178</v>
@@ -24618,7 +24617,7 @@
         <v>0</v>
       </c>
       <c r="BJ68" s="0">
-        <v>0.022111663902708662</v>
+        <v>0.022111663902708661</v>
       </c>
       <c r="BK68" s="0">
         <v>0</v>
@@ -25318,7 +25317,7 @@
         <v>0</v>
       </c>
       <c r="BB70" s="0">
-        <v>0.23654642223536349</v>
+        <v>0.23654642223536348</v>
       </c>
       <c r="BC70" s="0">
         <v>7.1356018283392517</v>
@@ -25536,7 +25535,7 @@
         <v>0.63545463040837247</v>
       </c>
       <c r="F71" s="0">
-        <v>0.69725402427476913</v>
+        <v>0.69725402427476912</v>
       </c>
       <c r="G71" s="0">
         <v>0.32051282051282021</v>
@@ -25803,7 +25802,7 @@
         <v>0</v>
       </c>
       <c r="CQ71" s="0">
-        <v>3.9986996098829613</v>
+        <v>3.9986996098829612</v>
       </c>
       <c r="CR71" s="0">
         <v>0</v>
@@ -26572,7 +26571,7 @@
         <v>11.551474142097621</v>
       </c>
       <c r="DF73" s="0">
-        <v>2.1472392638036793</v>
+        <v>2.1472392638036792</v>
       </c>
       <c r="DG73" s="0">
         <v>0</v>
@@ -27170,7 +27169,7 @@
         <v>0.27017899358324871</v>
       </c>
       <c r="BP75" s="0">
-        <v>0.022045855379188691</v>
+        <v>0.02204585537918869</v>
       </c>
       <c r="BQ75" s="0">
         <v>0.64608758076094708</v>
@@ -27245,13 +27244,13 @@
         <v>0</v>
       </c>
       <c r="CO75" s="0">
-        <v>0.13224014810896576</v>
+        <v>0.13224014810896575</v>
       </c>
       <c r="CP75" s="0">
         <v>0.01199184554502937</v>
       </c>
       <c r="CQ75" s="0">
-        <v>6.8433029908972634</v>
+        <v>6.8433029908972633</v>
       </c>
       <c r="CR75" s="0">
         <v>0.15979546180888449</v>
@@ -27278,7 +27277,7 @@
         <v>10.697787503039134</v>
       </c>
       <c r="CZ75" s="0">
-        <v>5.0570962479608435</v>
+        <v>5.0570962479608434</v>
       </c>
       <c r="DA75" s="0">
         <v>0</v>
@@ -27346,7 +27345,7 @@
         <v>9.4196804037005801</v>
       </c>
       <c r="F76" s="0">
-        <v>8.6252905225101078</v>
+        <v>8.6252905225101077</v>
       </c>
       <c r="G76" s="0">
         <v>10.336538461538451</v>
@@ -27592,7 +27591,7 @@
         <v>0.033277870216306127</v>
       </c>
       <c r="CJ76" s="0">
-        <v>0.031625553447185297</v>
+        <v>0.031625553447185296</v>
       </c>
       <c r="CK76" s="0">
         <v>1.2005108556832684</v>
@@ -27685,7 +27684,7 @@
         <v>0</v>
       </c>
       <c r="DO76" s="0">
-        <v>0.97087378640776601</v>
+        <v>0.970873786407766</v>
       </c>
       <c r="DP76" s="0">
         <v>0</v>
@@ -27711,7 +27710,7 @@
         <v>4.3987260049926791</v>
       </c>
       <c r="G77" s="0">
-        <v>5.6891025641025586</v>
+        <v>5.6891025641025585</v>
       </c>
       <c r="H77" s="0">
         <v>10.202845897668777</v>
@@ -27750,7 +27749,7 @@
         <v>9.7102256896071246</v>
       </c>
       <c r="T77" s="0">
-        <v>4.5277607047736082</v>
+        <v>4.5277607047736081</v>
       </c>
       <c r="U77" s="0">
         <v>3.6252091466815362</v>
@@ -27897,7 +27896,7 @@
         <v>0.19841269841269824</v>
       </c>
       <c r="BQ77" s="0">
-        <v>7.5735821966977675</v>
+        <v>7.5735821966977674</v>
       </c>
       <c r="BR77" s="0">
         <v>9.8813271978687247</v>
@@ -28073,7 +28072,7 @@
         <v>1.317035379185675</v>
       </c>
       <c r="G78" s="0">
-        <v>1.8028846153846137</v>
+        <v>1.8028846153846136</v>
       </c>
       <c r="H78" s="0">
         <v>6.0551014229488294</v>
@@ -28235,7 +28234,7 @@
         <v>7.7309236947791096</v>
       </c>
       <c r="BI78" s="0">
-        <v>0.032275416890801476</v>
+        <v>0.032275416890801475</v>
       </c>
       <c r="BJ78" s="0">
         <v>0.13266998341625194</v>
@@ -28331,7 +28330,7 @@
         <v>0.035893754486719283</v>
       </c>
       <c r="CO78" s="0">
-        <v>7.8682888124834634</v>
+        <v>7.8682888124834633</v>
       </c>
       <c r="CP78" s="0">
         <v>1.1152416356877313</v>
@@ -28444,7 +28443,7 @@
         <v>1.1295681063122913</v>
       </c>
       <c r="J79" s="0">
-        <v>2.7431421446384015</v>
+        <v>2.7431421446384014</v>
       </c>
       <c r="K79" s="0">
         <v>0</v>
@@ -28483,7 +28482,7 @@
         <v>0.55147058823529371</v>
       </c>
       <c r="W79" s="0">
-        <v>9.5384615384615295</v>
+        <v>9.5384615384615294</v>
       </c>
       <c r="X79" s="0">
         <v>6.8789084707219947</v>
@@ -28633,7 +28632,7 @@
         <v>10.836937166115483</v>
       </c>
       <c r="BU79" s="0">
-        <v>6.4034815045072993</v>
+        <v>6.4034815045072992</v>
       </c>
       <c r="BV79" s="0">
         <v>0.34398034398034366</v>
@@ -28648,7 +28647,7 @@
         <v>10.785953177257515</v>
       </c>
       <c r="BZ79" s="0">
-        <v>3.4755134281200602</v>
+        <v>3.4755134281200601</v>
       </c>
       <c r="CA79" s="0">
         <v>13.082706766917282</v>
@@ -28669,7 +28668,7 @@
         <v>0</v>
       </c>
       <c r="CG79" s="0">
-        <v>9.4664066654848345</v>
+        <v>9.4664066654848344</v>
       </c>
       <c r="CH79" s="0">
         <v>0.092752086921955662</v>
@@ -28684,7 +28683,7 @@
         <v>11.409110259684962</v>
       </c>
       <c r="CL79" s="0">
-        <v>2.9935581659719564</v>
+        <v>2.9935581659719563</v>
       </c>
       <c r="CM79" s="0">
         <v>10.78814980435997</v>
@@ -28699,7 +28698,7 @@
         <v>3.7534476555941922</v>
       </c>
       <c r="CQ79" s="0">
-        <v>0.032509752925877739</v>
+        <v>0.032509752925877738</v>
       </c>
       <c r="CR79" s="0">
         <v>12.144455097475221</v>
@@ -28914,16 +28913,16 @@
         <v>0.79365079365079294</v>
       </c>
       <c r="AT80" s="0">
-        <v>1.6694490818030035</v>
+        <v>1.6694490818030034</v>
       </c>
       <c r="AU80" s="0">
         <v>0.90875370919881227</v>
       </c>
       <c r="AV80" s="0">
-        <v>0.87189805499664586</v>
+        <v>0.87189805499664585</v>
       </c>
       <c r="AW80" s="0">
-        <v>0.18837459634015053</v>
+        <v>0.18837459634015052</v>
       </c>
       <c r="AX80" s="0">
         <v>0.97234883014281281</v>
@@ -28998,7 +28997,7 @@
         <v>2.9841467205470908</v>
       </c>
       <c r="BV80" s="0">
-        <v>1.3267813267813256</v>
+        <v>1.3267813267813255</v>
       </c>
       <c r="BW80" s="0">
         <v>10.043859649122799</v>
@@ -29016,7 +29015,7 @@
         <v>9.7744360902255547</v>
       </c>
       <c r="CB80" s="0">
-        <v>8.5039370078740078</v>
+        <v>8.5039370078740077</v>
       </c>
       <c r="CC80" s="0">
         <v>1.3123359580052483</v>
@@ -29046,7 +29045,7 @@
         <v>10.472541507024257</v>
       </c>
       <c r="CL80" s="0">
-        <v>6.5744600227358792</v>
+        <v>6.5744600227358791</v>
       </c>
       <c r="CM80" s="0">
         <v>9.9496925656791415</v>
@@ -29085,7 +29084,7 @@
         <v>0.19175455417066137</v>
       </c>
       <c r="CY80" s="0">
-        <v>0.26744468757597834</v>
+        <v>0.26744468757597833</v>
       </c>
       <c r="CZ80" s="0">
         <v>1.747844325332089</v>
@@ -29282,7 +29281,7 @@
         <v>3.6721068249258124</v>
       </c>
       <c r="AV81" s="0">
-        <v>0.17885088307623504</v>
+        <v>0.17885088307623503</v>
       </c>
       <c r="AW81" s="0">
         <v>0.08073196986006452</v>
@@ -29363,7 +29362,7 @@
         <v>3.83292383292383</v>
       </c>
       <c r="BW81" s="0">
-        <v>8.9912280701754313</v>
+        <v>8.9912280701754312</v>
       </c>
       <c r="BX81" s="0">
         <v>8.6243163651661696</v>
@@ -29572,7 +29571,7 @@
         <v>0.25641025641025905</v>
       </c>
       <c r="X82" s="0">
-        <v>0.056850483229108025</v>
+        <v>0.056850483229108024</v>
       </c>
       <c r="Y82" s="0">
         <v>7.3113207547170553</v>
@@ -29620,7 +29619,7 @@
         <v>0.74142724745135147</v>
       </c>
       <c r="AN82" s="0">
-        <v>0.26075619295958547</v>
+        <v>0.26075619295958546</v>
       </c>
       <c r="AO82" s="0">
         <v>0</v>
@@ -29719,7 +29718,7 @@
         <v>4.9987280590181129</v>
       </c>
       <c r="BU82" s="0">
-        <v>0.34193347839602462</v>
+        <v>0.34193347839602461</v>
       </c>
       <c r="BV82" s="0">
         <v>8.20638820638829</v>
@@ -29767,7 +29766,7 @@
         <v>8.8551549652119821</v>
       </c>
       <c r="CK82" s="0">
-        <v>2.5968497232865318</v>
+        <v>2.5968497232865317</v>
       </c>
       <c r="CL82" s="0">
         <v>9.7385373247443212</v>
@@ -29788,7 +29787,7 @@
         <v>0</v>
       </c>
       <c r="CR82" s="0">
-        <v>3.1160115052732818</v>
+        <v>3.1160115052732817</v>
       </c>
       <c r="CS82" s="0">
         <v>0</v>
@@ -29958,7 +29957,7 @@
         <v>0</v>
       </c>
       <c r="AF83" s="0">
-        <v>2.105263157894735</v>
+        <v>2.1052631578947349</v>
       </c>
       <c r="AG83" s="0">
         <v>0</v>
@@ -30183,7 +30182,7 @@
         <v>0.62695924764890221</v>
       </c>
       <c r="DC83" s="0">
-        <v>0.20206555904804655</v>
+        <v>0.20206555904804654</v>
       </c>
       <c r="DD83" s="0">
         <v>0.34608378870673923</v>
@@ -30350,7 +30349,7 @@
         <v>0</v>
       </c>
       <c r="AP84" s="0">
-        <v>0.88300220750551795</v>
+        <v>0.88300220750551794</v>
       </c>
       <c r="AQ84" s="0">
         <v>0.2145922746781114</v>
@@ -30401,7 +30400,7 @@
         <v>0</v>
       </c>
       <c r="BG84" s="0">
-        <v>2.2181146025877983</v>
+        <v>2.2181146025877982</v>
       </c>
       <c r="BH84" s="0">
         <v>0.066934404283801818</v>
@@ -30473,7 +30472,7 @@
         <v>0</v>
       </c>
       <c r="CE84" s="0">
-        <v>1.3333333333333322</v>
+        <v>1.3333333333333321</v>
       </c>
       <c r="CF84" s="0">
         <v>5.0086355785837604</v>
@@ -30718,7 +30717,7 @@
         <v>0.042918454935622276</v>
       </c>
       <c r="AR85" s="0">
-        <v>0.037383177570093421</v>
+        <v>0.03738317757009342</v>
       </c>
       <c r="AS85" s="0">
         <v>7.1428571428571361</v>
@@ -31173,7 +31172,7 @@
         <v>2.4570024570024547</v>
       </c>
       <c r="BW86" s="0">
-        <v>0.043859649122806981</v>
+        <v>0.04385964912280698</v>
       </c>
       <c r="BX86" s="0">
         <v>0</v>
@@ -31245,7 +31244,7 @@
         <v>0</v>
       </c>
       <c r="CU86" s="0">
-        <v>4.491017964071852</v>
+        <v>4.4910179640718519</v>
       </c>
       <c r="CV86" s="0">
         <v>0</v>
@@ -31664,7 +31663,7 @@
         <v>1.4957264957264944</v>
       </c>
       <c r="DN87" s="0">
-        <v>0.58593749999999945</v>
+        <v>0.58593749999999944</v>
       </c>
       <c r="DO87" s="0">
         <v>0</v>
